--- a/analytics_report_2026-07.xlsx
+++ b/analytics_report_2026-07.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,6 +490,38 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>2026-07-12 15:04:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-07-13 17:35:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>51</v>
+      </c>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-07-21 12:49:13</t>
         </is>
       </c>
     </row>
@@ -504,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2081,6 +2113,251 @@
       <c r="G45" t="inlineStr">
         <is>
           <t>63FopFojG9UZgr6wF3ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>not selected</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>15f6e565-035d-42bc-b893-a7010b939736</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>not selected</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>user_profile</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>✨ Better Skin</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="n">
+        <v>46216.64930930555</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>8eASqF0mMMXcw05QAXfR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>not selected</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>bc2a952d-63c9-483f-9b84-f9eb330dd0e3</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>not selected</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>user_profile</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>🔋 增强精力</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="n">
+        <v>46218.02529880787</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>qdCSwfVcsF0i2T79OWTj</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>aa9dc6cf-f598-454a-93f2-7be6e8b493bf</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>👨 Male</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>user_profile</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>🔋 More Energy</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="n">
+        <v>46219.22447222222</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>uaExsmEbyi9plL3UtLEu</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>18-25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>83e570d2-6067-4df7-b699-25c7b5c8034d</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>👩 Female</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>user_profile</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>✨ Better Skin</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="n">
+        <v>46221.00451001157</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>QcCtikXNcoqQihxbGiex</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>not selected</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>73b64275-104a-4e5a-b8fe-7392447ea379</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>not selected</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>user_profile</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>💆 Stress Relief</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>46221.43697782407</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>yhTTU8NiDrHbFwmdqn9E</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>not selected</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2a691834-653c-4ba7-a215-eb6902fedb52</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>not selected</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>user_profile</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>💆 Stress Relief</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="n">
+        <v>46221.55619583333</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>KKrUlsK69qrzaH5XBfLM</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>18-25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>87354321-d499-4d4f-bb84-2752f17655ac</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>👨 Male</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>user_profile</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>😴 Better Sleep</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="n">
+        <v>46221.57383737269</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>OiD0Zve5Y1LVNEX4tOxH</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2567,25 +2844,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>032721e3-9dc9-48f7-9a08-4a06db10ff45</t>
+          <t>bc2a952d-63c9-483f-9b84-f9eb330dd0e3</t>
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46193.70412306713</v>
+        <v>46218.02599950232</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>who r u</t>
+          <t>Relelieve body stre and increase muscle mass</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Fitness</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7tSrI5PaQCDUWSddEAxY</t>
+          <t>6yYkT8Q6zCUdmvDNNB9m</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -2595,15 +2872,15 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3e24bebd-0a72-4c7b-86fe-c25cebc49f25</t>
+          <t>032721e3-9dc9-48f7-9a08-4a06db10ff45</t>
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46190.0910078588</v>
+        <v>46193.70412306713</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Herbal medicine</t>
+          <t>who r u</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2613,7 +2890,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9IAtLc49fwqL9ogN7yeR</t>
+          <t>7tSrI5PaQCDUWSddEAxY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -2623,15 +2900,15 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
+          <t>3e24bebd-0a72-4c7b-86fe-c25cebc49f25</t>
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46198.63558466435</v>
+        <v>46190.0910078588</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>suwen</t>
+          <t>Herbal medicine</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2641,7 +2918,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9KxHsF7Aew1iiNDBEo7l</t>
+          <t>9IAtLc49fwqL9ogN7yeR</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -2651,15 +2928,15 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>a15f9e96-cfbf-4495-86a3-e675b3cb4d52</t>
+          <t>2a691834-653c-4ba7-a215-eb6902fedb52</t>
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46194.16932476852</v>
+        <v>46221.55943049768</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kamu bisa matematika gak?</t>
+          <t>I already have 10 saunas</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2669,7 +2946,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9zI1RY1yrMy0h2DmIivX</t>
+          <t>9JQKlsnQ2zGNhtNgejLt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -2679,25 +2956,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>b401b461-2d7d-4f2b-95c1-55a1a16ef5c0</t>
+          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46187.45716660879</v>
+        <v>46198.63558466435</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Skincare tips</t>
+          <t>suwen</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Skincare</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>A23O64w8fnzlWs3d2IVN</t>
+          <t>9KxHsF7Aew1iiNDBEo7l</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -2707,15 +2984,15 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>e77acc12-4383-4321-914a-555372755dbc</t>
+          <t>a15f9e96-cfbf-4495-86a3-e675b3cb4d52</t>
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46184.06269796296</v>
+        <v>46194.16932476852</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>How about feasting</t>
+          <t>Kamu bisa matematika gak?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2725,7 +3002,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BrM2AsZxgPCv4MhNWTcq</t>
+          <t>9zI1RY1yrMy0h2DmIivX</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -2735,49 +3012,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>INTEGRATION-TEST-156f926d</t>
+          <t>b401b461-2d7d-4f2b-95c1-55a1a16ef5c0</t>
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46196.20574025463</v>
+        <v>46187.45716660879</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Best recipe for protein-rich diet.</t>
+          <t>Skincare tips</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Nutrition</t>
+          <t>Skincare</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CTBAj7FJptAi3p05yINX</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>A well-planned protein-rich diet can be beneficial...</t>
-        </is>
-      </c>
-      <c r="G23" t="b">
-        <v>1</v>
-      </c>
+          <t>A23O64w8fnzlWs3d2IVN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>956a919b-c897-4c88-b2a9-d85623ca2132</t>
+          <t>2a691834-653c-4ba7-a215-eb6902fedb52</t>
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46202.18734961806</v>
+        <v>46221.5564478125</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Who r u</t>
+          <t>I finished sauna and feel good</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2787,7 +3058,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>EDTPWlJjjy4PKQ0JHZ4t</t>
+          <t>AjsvxC2s61ojHfN7iZ3C</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -2797,15 +3068,15 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
+          <t>87354321-d499-4d4f-bb84-2752f17655ac</t>
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46198.63945668982</v>
+        <v>46221.57517351852</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>any recommendation for tcm</t>
+          <t>Are u run on gpt</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2815,7 +3086,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ESkdlBL3853B1JmSi2bC</t>
+          <t>B8DeknAtvEBK2v1l3vsk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -2825,49 +3096,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>INTEGRATION-TEST-ecf6da81</t>
+          <t>e77acc12-4383-4321-914a-555372755dbc</t>
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46191.24342388889</v>
+        <v>46184.06269796296</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Best recipe for protein-rich diet.</t>
+          <t>How about feasting</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Nutrition</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ETdsdWkBTWJP9lMzJOnk</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>A protein-rich diet can be achieved through a vari...</t>
-        </is>
-      </c>
-      <c r="G26" t="b">
-        <v>1</v>
-      </c>
+          <t>BrM2AsZxgPCv4MhNWTcq</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
+          <t>bc2a952d-63c9-483f-9b84-f9eb330dd0e3</t>
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46198.64115482639</v>
+        <v>46218.02724184027</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>where do u obtain the list</t>
+          <t>Pain killer</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2877,7 +3142,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>EVX7LrDzp4Y85OjVzmrX</t>
+          <t>BzeS1ZmS2LOy1nKTgtW0</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -2887,77 +3152,77 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
+          <t>INTEGRATION-TEST-156f926d</t>
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46198.6454865162</v>
+        <v>46196.20574025463</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Give me TCM skincare advice.</t>
+          <t>Best recipe for protein-rich diet.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Skincare</t>
+          <t>Nutrition</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ef7HYaKoicnVKQJVbOSg</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+          <t>CTBAj7FJptAi3p05yINX</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>A well-planned protein-rich diet can be beneficial...</t>
+        </is>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>INTEGRATION-TEST-037cf480</t>
+          <t>bc2a952d-63c9-483f-9b84-f9eb330dd0e3</t>
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46174.68950780093</v>
+        <v>46218.02882723379</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Best recipe for protein-rich diet.</t>
+          <t>Pls share brand name</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nutrition</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Em5K4Mvz0WkcxCJMHXxr</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>A protein-rich diet is essential for building and ...</t>
-        </is>
-      </c>
-      <c r="G29" t="b">
-        <v>1</v>
-      </c>
+          <t>DP6yQBG7aRgjG97XSAhn</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>58d8b5a2-c708-4447-a51d-09280a5fb3e4</t>
+          <t>956a919b-c897-4c88-b2a9-d85623ca2132</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46200.1091655787</v>
+        <v>46202.18734961806</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>who r u</t>
+          <t>Who r u</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2967,7 +3232,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>G9vsn9mZIgknVzYFVwWp</t>
+          <t>EDTPWlJjjy4PKQ0JHZ4t</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -2977,15 +3242,15 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1de3f616-ad83-4a51-9d26-9c38b691c7d9</t>
+          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46193.45997763889</v>
+        <v>46198.63945668982</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>what do u do</t>
+          <t>any recommendation for tcm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2995,7 +3260,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GHgWV2teXHdxOkKe3Idv</t>
+          <t>ESkdlBL3853B1JmSi2bC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -3005,79 +3270,87 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>b53ff878-1e66-4f1a-95f1-64c8c8fc8b17</t>
+          <t>INTEGRATION-TEST-ecf6da81</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46215.14981611111</v>
+        <v>46191.24342388889</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pls recommend any over the counter capsule </t>
+          <t>Best recipe for protein-rich diet.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Nutrition</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HlpdO7PE9JXeJxyxwToH</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+          <t>ETdsdWkBTWJP9lMzJOnk</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>A protein-rich diet can be achieved through a vari...</t>
+        </is>
+      </c>
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FINAL-PROOFS-94e270</t>
+          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46175.33286694445</v>
+        <v>46198.64115482639</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>User Test A: Skincare glow</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>where do u obtain the list</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ho5Gsnat0dl0Rr7RE4od</t>
+          <t>EVX7LrDzp4Y85OjVzmrX</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="b">
-        <v>1</v>
-      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>b53ff878-1e66-4f1a-95f1-64c8c8fc8b17</t>
+          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46215.14004230324</v>
+        <v>46198.6454865162</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Who r u</t>
+          <t>Give me TCM skincare advice.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Skincare</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hsl8p0koVN5qLfjeMdVO</t>
+          <t>Ef7HYaKoicnVKQJVbOSg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -3087,25 +3360,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>295fd48f-4458-4630-b615-5bdfdd20090e</t>
+          <t>2a691834-653c-4ba7-a215-eb6902fedb52</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46183.65018125</v>
+        <v>46221.56017597222</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>How does my COMT variation affect my Liver Qi stagnation</t>
+          <t>How it help skin</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TCM</t>
+          <t>Skincare</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>I3SDEZsGRAmj7MPlBjXO</t>
+          <t>Em0nTUOI42EILdQd4fos</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -3115,15 +3388,15 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>956a919b-c897-4c88-b2a9-d85623ca2132</t>
+          <t>INTEGRATION-TEST-037cf480</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46202.18842942129</v>
+        <v>46174.68950780093</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>How much protein power consumer daily</t>
+          <t>Best recipe for protein-rich diet.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3133,31 +3406,41 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>IGqrD2hob1oB3a8QNAnK</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+          <t>Em5K4Mvz0WkcxCJMHXxr</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>A protein-rich diet is essential for building and ...</t>
+        </is>
+      </c>
+      <c r="G36" t="b">
+        <v>1</v>
+      </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DEBUG_123</t>
+          <t>58d8b5a2-c708-4447-a51d-09280a5fb3e4</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46174.74240986111</v>
+        <v>46200.1091655787</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DEBUG_LIVE_CHAT_TEST</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>who r u</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IcLwh83uKOYCg7dRtm7H</t>
+          <t>G9vsn9mZIgknVzYFVwWp</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -3167,15 +3450,15 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
+          <t>1de3f616-ad83-4a51-9d26-9c38b691c7d9</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46198.64495980324</v>
+        <v>46193.45997763889</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>can i upload the file</t>
+          <t>what do u do</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3185,7 +3468,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IkD0eYm3Gb36tHHkbuYV</t>
+          <t>GHgWV2teXHdxOkKe3Idv</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -3195,15 +3478,15 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>d0233369-eb1e-4a89-aa5e-47c5296a9ccf</t>
+          <t>87354321-d499-4d4f-bb84-2752f17655ac</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46207.24548171296</v>
+        <v>46221.5744647338</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mengatasi kulit kusam</t>
+          <t>How to strengthen kidney and liver</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3213,7 +3496,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>IvStxzM57yBWvmdnCUg9</t>
+          <t>GzjYobNVcJLyRE1W0UQ8</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -3227,11 +3510,11 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46215.1473912037</v>
+        <v>46215.14981611111</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>It's not specific to target minimize regrow cancer cell. Isn't it</t>
+          <t xml:space="preserve">Pls recommend any over the counter capsule </t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3241,7 +3524,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>K9mzgIH9nPOJE0o9OKha</t>
+          <t>HlpdO7PE9JXeJxyxwToH</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -3251,53 +3534,51 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0a8d4f3a-37a3-41cb-b712-b4dcf9161966</t>
+          <t>FINAL-PROOFS-94e270</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46180.16048909722</v>
+        <v>46175.33286694445</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hi, aku mau tau dong manfaat sauna buat tubuh apa aja</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
+          <t>User Test A: Skincare glow</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kw04PA6pEkZ4TiHVofjx</t>
+          <t>Ho5Gsnat0dl0Rr7RE4od</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>84d8c46c-237e-49f0-be59-6123c64d1957</t>
+          <t>b53ff878-1e66-4f1a-95f1-64c8c8fc8b17</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46193.45156292824</v>
+        <v>46215.14004230324</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tell me about the Bencao Gangmu herb encyclopedia.</t>
+          <t>Who r u</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TCM</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>L4Ufdgbk4qBvz13tMl9H</t>
+          <t>Hsl8p0koVN5qLfjeMdVO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -3307,25 +3588,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>e77acc12-4383-4321-914a-555372755dbc</t>
+          <t>295fd48f-4458-4630-b615-5bdfdd20090e</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46184.06304063657</v>
+        <v>46183.65018125</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>16 hours fasting?</t>
+          <t>How does my COMT variation affect my Liver Qi stagnation</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>TCM</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LA2WqrqD0Ov8OmrwoR8H</t>
+          <t>I3SDEZsGRAmj7MPlBjXO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -3335,25 +3616,25 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>d0233369-eb1e-4a89-aa5e-47c5296a9ccf</t>
+          <t>bc2a952d-63c9-483f-9b84-f9eb330dd0e3</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46207.24477123842</v>
+        <v>46218.02752582176</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Give me TCM skincare advice.</t>
+          <t>Who r u</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Skincare</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MdNnZsaXK2F0GnJY0Ufa</t>
+          <t>IGXYvfTDiDjPrNTNo4cw</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -3363,25 +3644,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>536f5a2e-ab6b-4e3b-89a7-dfcf201b4b3d</t>
+          <t>956a919b-c897-4c88-b2a9-d85623ca2132</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46179.40605415509</v>
+        <v>46202.18842942129</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>skincare</t>
+          <t>How much protein power consumer daily</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Skincare</t>
+          <t>Nutrition</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NYRrVHbmxA6fy1VeU9fE</t>
+          <t>IGqrD2hob1oB3a8QNAnK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -3391,25 +3672,21 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>b53ff878-1e66-4f1a-95f1-64c8c8fc8b17</t>
+          <t>DEBUG_123</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46215.14564487268</v>
+        <v>46174.74240986111</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Your recommendation is too gemeral</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
+          <t>DEBUG_LIVE_CHAT_TEST</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>NmdyeG18bXR94X7gKP4v</t>
+          <t>IcLwh83uKOYCg7dRtm7H</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -3419,51 +3696,53 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FINAL-PROOFS-3dc819</t>
+          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46196.20586653935</v>
+        <v>46198.64495980324</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>User Test B: TCM Herbs</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>can i upload the file</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>O52WCFX9mMKpgpIEAw60</t>
+          <t>IkD0eYm3Gb36tHHkbuYV</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="b">
-        <v>1</v>
-      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>956a919b-c897-4c88-b2a9-d85623ca2132</t>
+          <t>d0233369-eb1e-4a89-aa5e-47c5296a9ccf</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46202.19003054398</v>
+        <v>46207.24548171296</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">How about vitamin </t>
+          <t>Mengatasi kulit kusam</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Nutrition</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OsCdsGu8QMMVXi951Y7Z</t>
+          <t>IvStxzM57yBWvmdnCUg9</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -3473,25 +3752,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>32b2520b-8f50-4e3e-8764-145bb851a8c4</t>
+          <t>b53ff878-1e66-4f1a-95f1-64c8c8fc8b17</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46186.25995912037</v>
+        <v>46215.1473912037</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>u can also utilize this tech and algorithm to tackle skin care issue?</t>
+          <t>It's not specific to target minimize regrow cancer cell. Isn't it</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Skincare</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PBA3KZcc6mJgTvC8HV3I</t>
+          <t>K9mzgIH9nPOJE0o9OKha</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -3501,25 +3780,25 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>e77acc12-4383-4321-914a-555372755dbc</t>
+          <t>0a8d4f3a-37a3-41cb-b712-b4dcf9161966</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46184.06353392361</v>
+        <v>46180.16048909722</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>How about protein power</t>
+          <t>Hi, aku mau tau dong manfaat sauna buat tubuh apa aja</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Nutrition</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PjUxuuYryYxXunBYH19a</t>
+          <t>Kw04PA6pEkZ4TiHVofjx</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -3529,25 +3808,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>f4f764ab-bd03-4c89-879f-73a8a455d913</t>
+          <t>84d8c46c-237e-49f0-be59-6123c64d1957</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46182.09221469907</v>
+        <v>46193.45156292824</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Booat vitality </t>
+          <t>Tell me about the Bencao Gangmu herb encyclopedia.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>TCM</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>QM2W50WM0tdzSTwJxfgD</t>
+          <t>L4Ufdgbk4qBvz13tMl9H</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -3557,15 +3836,15 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
+          <t>e77acc12-4383-4321-914a-555372755dbc</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46198.63151245371</v>
+        <v>46184.06304063657</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>what is yello emperor inner cannon</t>
+          <t>16 hours fasting?</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3575,7 +3854,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Qav9m8mENrTAlMbWF1m6</t>
+          <t>LA2WqrqD0Ov8OmrwoR8H</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -3585,25 +3864,25 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>63efd30d-8437-4c0f-ab65-fb29fd5c96d8</t>
+          <t>d0233369-eb1e-4a89-aa5e-47c5296a9ccf</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46193.70200883102</v>
+        <v>46207.24477123842</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>who r u</t>
+          <t>Give me TCM skincare advice.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Skincare</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>R3yuCzZfEchRlk6N4oxv</t>
+          <t>MdNnZsaXK2F0GnJY0Ufa</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -3613,25 +3892,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>f3d7c818-72a3-4e88-aa0a-974b6c7c743d</t>
+          <t>536f5a2e-ab6b-4e3b-89a7-dfcf201b4b3d</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46199.4950289699</v>
+        <v>46179.40605415509</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Help me discover my TCM body constitution type.</t>
+          <t>skincare</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wellness</t>
+          <t>Skincare</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RYRaQxaO2hgFh2nV72rO</t>
+          <t>NYRrVHbmxA6fy1VeU9fE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -3641,15 +3920,15 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2905fb07-918f-4c60-9954-1a68b01a1e7a</t>
+          <t>b53ff878-1e66-4f1a-95f1-64c8c8fc8b17</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46202.18895690973</v>
+        <v>46215.14564487268</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>tanggan kesemutan bangun tidur, kenapa?</t>
+          <t>Your recommendation is too gemeral</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3659,7 +3938,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RjHsO7eiLBA0n8ZCwAee</t>
+          <t>NmdyeG18bXR94X7gKP4v</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -3669,25 +3948,25 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>d0233369-eb1e-4a89-aa5e-47c5296a9ccf</t>
+          <t>15f6e565-035d-42bc-b893-a7010b939736</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46207.24775020833</v>
+        <v>46216.65033270833</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bagaimana dengan inject untuk acne</t>
+          <t xml:space="preserve">Toner cosrx ceramide bisa di pakai setiap hari gak </t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Skincare</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RmqoJG1ND5zJl3qSlSkb</t>
+          <t>NyhRCXEWCQCMDdTqmN8C</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -3697,53 +3976,51 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>d5f0fcb3-a208-475d-a849-f4daf69af0c2</t>
+          <t>FINAL-PROOFS-3dc819</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46179.42006091435</v>
+        <v>46196.20586653935</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Who r u</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
+          <t>User Test B: TCM Herbs</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>S6K136xQ23BBueeJXAdQ</t>
+          <t>O52WCFX9mMKpgpIEAw60</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>d0233369-eb1e-4a89-aa5e-47c5296a9ccf</t>
+          <t>956a919b-c897-4c88-b2a9-d85623ca2132</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>46207.24906013889</v>
+        <v>46202.19003054398</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bagaimana dengan salmon dna?</t>
+          <t xml:space="preserve">How about vitamin </t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Nutrition</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>TCY2vhK9CsUOTppGQWOt</t>
+          <t>OsCdsGu8QMMVXi951Y7Z</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -3753,25 +4030,25 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
+          <t>32b2520b-8f50-4e3e-8764-145bb851a8c4</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>46198.64281020833</v>
+        <v>46186.25995912037</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>you are nutribot... can you recommend how chinese doctor use nutribot</t>
+          <t>u can also utilize this tech and algorithm to tackle skin care issue?</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Skincare</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UhFtVawlXx7rEEJgapYP</t>
+          <t>PBA3KZcc6mJgTvC8HV3I</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -3781,15 +4058,15 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>58218d11-8e3c-49f4-b44e-df2749f944c3</t>
+          <t>15f6e565-035d-42bc-b893-a7010b939736</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>46199.33285601852</v>
+        <v>46216.64969662037</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Give me personalized nutrition advice based on TCM.</t>
+          <t>Ceramide toner bisa di kombinasi sama retinol serum gak</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3799,7 +4076,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>VFqEUZudQCW1KmgejAzs</t>
+          <t>PL6ZwvuDeyvAFkNsDio2</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -3809,25 +4086,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>21f9db7c-a652-4de3-baf2-9997b2e598bf</t>
+          <t>e77acc12-4383-4321-914a-555372755dbc</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>46175.33340519676</v>
+        <v>46184.06353392361</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>i need tcm advice for vatality</t>
+          <t>How about protein power</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Nutrition</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>XXhMbVB4CHRycpZHWm6Q</t>
+          <t>PjUxuuYryYxXunBYH19a</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -3837,15 +4114,15 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>58218d11-8e3c-49f4-b44e-df2749f944c3</t>
+          <t>f4f764ab-bd03-4c89-879f-73a8a455d913</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>46199.33291730324</v>
+        <v>46182.09221469907</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>who r u</t>
+          <t xml:space="preserve">Booat vitality </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3855,7 +4132,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>XxWEwoeCr96G8BXJW0oh</t>
+          <t>QM2W50WM0tdzSTwJxfgD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -3865,15 +4142,15 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>070e6c82-3135-4bdc-9341-55a8feb109b8</t>
+          <t>87354321-d499-4d4f-bb84-2752f17655ac</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>46193.70126134259</v>
+        <v>46221.57400293981</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>lost weight</t>
+          <t>How to reduce white hair</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3883,7 +4160,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Y1aTLxRUqm58bNAeNleQ</t>
+          <t>QTVfkXd9RXslFUchNdMh</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -3897,11 +4174,11 @@
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>46198.63127357639</v>
+        <v>46198.63151245371</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>who r u</t>
+          <t>what is yello emperor inner cannon</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3911,7 +4188,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>YYtYfSS1iVfSfPAJzhnR</t>
+          <t>Qav9m8mENrTAlMbWF1m6</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -3921,15 +4198,15 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>91fb92a5-4834-487e-a265-e00450ba538b</t>
+          <t>63efd30d-8437-4c0f-ab65-fb29fd5c96d8</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>46201.20854417824</v>
+        <v>46193.70200883102</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Vit D3 200 iu</t>
+          <t>who r u</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3939,7 +4216,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Yv3jMACjaO3dmK1DdTwB</t>
+          <t>R3yuCzZfEchRlk6N4oxv</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -3949,25 +4226,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>536f5a2e-ab6b-4e3b-89a7-dfcf201b4b3d</t>
+          <t>f3d7c818-72a3-4e88-aa0a-974b6c7c743d</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>46179.40940675926</v>
+        <v>46199.4950289699</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>i want lose weight plan</t>
+          <t>Help me discover my TCM body constitution type.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Wellness</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Z59tApvVw6tlz1AvJiFl</t>
+          <t>RYRaQxaO2hgFh2nV72rO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -3977,15 +4254,15 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
+          <t>2905fb07-918f-4c60-9954-1a68b01a1e7a</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>46198.64311140047</v>
+        <v>46202.18895690973</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>why people trust nutribot if they can consult doctor</t>
+          <t>tanggan kesemutan bangun tidur, kenapa?</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3995,7 +4272,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ZeFoQUoXhu8ahGJSn9Cq</t>
+          <t>RjHsO7eiLBA0n8ZCwAee</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -4005,25 +4282,25 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>b53ff878-1e66-4f1a-95f1-64c8c8fc8b17</t>
+          <t>d0233369-eb1e-4a89-aa5e-47c5296a9ccf</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>46215.1416365162</v>
+        <v>46207.24775020833</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Can I take creatine everyday </t>
+          <t>Bagaimana dengan inject untuk acne</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Skincare</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ZkJd7czGgXms8q7MU98Y</t>
+          <t>RmqoJG1ND5zJl3qSlSkb</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -4033,16 +4310,15 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>64a4b397-aada-4511-b117-32cfd0338ff9</t>
+          <t>d5f0fcb3-a208-475d-a849-f4daf69af0c2</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>46185.42890658565</v>
+        <v>46179.42006091435</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Aku sangat stres dan 
-tidak bisa tidur, tolong bantu aku</t>
+          <t>Who r u</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4052,7 +4328,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>a5xmTEKDJdrnVuE7i3fQ</t>
+          <t>S6K136xQ23BBueeJXAdQ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -4062,41 +4338,43 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FINAL-PROOFS-94e270</t>
+          <t>bc2a952d-63c9-483f-9b84-f9eb330dd0e3</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>46175.33286894676</v>
+        <v>46218.02691515046</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>User Test B: TCM Herbs</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>Any vitamin</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Nutrition</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>aNaSBWbMpITKXaqYq8r3</t>
+          <t>T7U2ArMALj43rbfUw8Xj</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="b">
-        <v>1</v>
-      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
+          <t>d0233369-eb1e-4a89-aa5e-47c5296a9ccf</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>46198.64384791667</v>
+        <v>46207.24906013889</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>can i provide you result of dna</t>
+          <t>Bagaimana dengan salmon dna?</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4106,7 +4384,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>bMY9FIOFT6mngIAKeOLK</t>
+          <t>TCY2vhK9CsUOTppGQWOt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -4116,49 +4394,43 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>INTEGRATION-TEST-ecf6da81</t>
+          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>46191.24336759259</v>
+        <v>46198.64281020833</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>My skin is glowing but a bit dry.</t>
+          <t>you are nutribot... can you recommend how chinese doctor use nutribot</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Skincare</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>bZ6ldGiwRUeaOQxEUikZ</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>It sounds like you're experiencing a common issue ...</t>
-        </is>
-      </c>
-      <c r="G72" t="b">
-        <v>1</v>
-      </c>
+          <t>UhFtVawlXx7rEEJgapYP</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6ec64ea4-cada-4c15-b707-757d3f3e9db0</t>
+          <t>58218d11-8e3c-49f4-b44e-df2749f944c3</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>46180.10743871528</v>
+        <v>46199.33285601852</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>obat untuk dada sesak</t>
+          <t>Give me personalized nutrition advice based on TCM.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4168,7 +4440,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>c4qAav6T0rFA4KDMYBNA</t>
+          <t>VFqEUZudQCW1KmgejAzs</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -4178,15 +4450,15 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>INTEGRATION-TEST-037cf480</t>
+          <t>21f9db7c-a652-4de3-baf2-9997b2e598bf</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>46174.68946401621</v>
+        <v>46175.33340519676</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>What is the Five Elements theory?</t>
+          <t>i need tcm advice for vatality</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4196,31 +4468,25 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>cCea6KJFzQYJOyYaq01i</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>The Five Elements theory, also known as the Wǔ Xín...</t>
-        </is>
-      </c>
-      <c r="G74" t="b">
-        <v>1</v>
-      </c>
+          <t>XXhMbVB4CHRycpZHWm6Q</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>9d654e7d-0bd3-4e56-bbef-67e80a6c5bba</t>
+          <t>58218d11-8e3c-49f4-b44e-df2749f944c3</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>46201.20408241898</v>
+        <v>46199.33291730324</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">What about vit A </t>
+          <t>who r u</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4230,7 +4496,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>cFs9yf6FdLtmUDn0yzio</t>
+          <t>XxWEwoeCr96G8BXJW0oh</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -4240,15 +4506,15 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>c1e37346-80ed-42b1-af0c-3f2326dc64a0</t>
+          <t>070e6c82-3135-4bdc-9341-55a8feb109b8</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>46206.06898725694</v>
+        <v>46193.70126134259</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">tengan kesemutan saat bangun tidur </t>
+          <t>lost weight</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4258,7 +4524,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>cXWUiKLun35np6sqtwOD</t>
+          <t>Y1aTLxRUqm58bNAeNleQ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -4272,11 +4538,11 @@
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>46198.64090936343</v>
+        <v>46198.63127357639</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>pls provide the name; address...of the chinese medicine</t>
+          <t>who r u</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4286,7 +4552,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ctxqIMddNj6ZMkMe2kf7</t>
+          <t>YYtYfSS1iVfSfPAJzhnR</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -4296,15 +4562,15 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
+          <t>91fb92a5-4834-487e-a265-e00450ba538b</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>46198.64174096065</v>
+        <v>46201.20854417824</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>wfcms</t>
+          <t>Vit D3 200 iu</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4314,7 +4580,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>eLZLWRCYdPofgv8DKCsL</t>
+          <t>Yv3jMACjaO3dmK1DdTwB</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -4324,15 +4590,15 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>56aab1b5-d73a-4a2e-b431-73b54989e343</t>
+          <t>536f5a2e-ab6b-4e3b-89a7-dfcf201b4b3d</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>46194.15376690972</v>
+        <v>46179.40940675926</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">kulit berjerawat </t>
+          <t>i want lose weight plan</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4342,7 +4608,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>eOP0CDKDr1Cou5QeS1jx</t>
+          <t>Z59tApvVw6tlz1AvJiFl</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -4352,15 +4618,15 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>b53ff878-1e66-4f1a-95f1-64c8c8fc8b17</t>
+          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>46215.14854802084</v>
+        <v>46198.64311140047</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Can u check where I get get those herba, in bandung, Indonesia</t>
+          <t>why people trust nutribot if they can consult doctor</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4370,7 +4636,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>fJH84CXQYXQjuhT9uS1B</t>
+          <t>ZeFoQUoXhu8ahGJSn9Cq</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -4380,25 +4646,25 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>956a919b-c897-4c88-b2a9-d85623ca2132</t>
+          <t>b53ff878-1e66-4f1a-95f1-64c8c8fc8b17</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>46202.18764390046</v>
+        <v>46215.1416365162</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>I need to gain muscle weight and strength for 50+ years old male</t>
+          <t xml:space="preserve">Can I take creatine everyday </t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Fitness</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>fWd6DNNDU8ZDHE3Z4xQK</t>
+          <t>ZkJd7czGgXms8q7MU98Y</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -4408,15 +4674,16 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>956a919b-c897-4c88-b2a9-d85623ca2132</t>
+          <t>64a4b397-aada-4511-b117-32cfd0338ff9</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>46202.19071785879</v>
+        <v>46185.42890658565</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>If I always feel fatigue, what bit shall I take</t>
+          <t>Aku sangat stres dan 
+tidak bisa tidur, tolong bantu aku</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4426,7 +4693,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>fe475cgH4urufBe4SydB</t>
+          <t>a5xmTEKDJdrnVuE7i3fQ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -4436,43 +4703,41 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
+          <t>FINAL-PROOFS-94e270</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>46198.63177532407</v>
+        <v>46175.33286894676</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>what is five elements related to health</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
+          <t>User Test B: TCM Herbs</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>fzjPVCi6bAoTZGGjphQT</t>
+          <t>aNaSBWbMpITKXaqYq8r3</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="H83" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>a3724450-b056-4cb5-a036-f033607ecbc9</t>
+          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>46180.13959449074</v>
+        <v>46198.64384791667</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>how can you help</t>
+          <t>can i provide you result of dna</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4482,7 +4747,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>gaQg4g4u1ZGnzwcNBr1n</t>
+          <t>bMY9FIOFT6mngIAKeOLK</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -4492,53 +4757,59 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0677f4bc-fa87-4e06-8849-4d6ddf468086</t>
+          <t>INTEGRATION-TEST-ecf6da81</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>46179.39384826389</v>
+        <v>46191.24336759259</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>who r u</t>
+          <t>My skin is glowing but a bit dry.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Skincare</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>gkc0ghq7rOho0OS5CtXK</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
+          <t>bZ6ldGiwRUeaOQxEUikZ</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>It sounds like you're experiencing a common issue ...</t>
+        </is>
+      </c>
+      <c r="G85" t="b">
+        <v>1</v>
+      </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>b53ff878-1e66-4f1a-95f1-64c8c8fc8b17</t>
+          <t>aa9dc6cf-f598-454a-93f2-7be6e8b493bf</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>46215.14050265047</v>
+        <v>46219.22470755787</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Can I don sauna before meal in the morning. And body feel tired from gym </t>
+          <t>Are u optimal today</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Fitness</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>gnQL0z2SIUqozsXDBZCq</t>
+          <t>beVFd8rO5hApWIH9OoQS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -4548,15 +4819,15 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
+          <t>6ec64ea4-cada-4c15-b707-757d3f3e9db0</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
-        <v>46198.63743409723</v>
+        <v>46180.10743871528</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>your suggestion is too general</t>
+          <t>obat untuk dada sesak</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4566,7 +4837,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>hISonSUrOOGJppSb3otv</t>
+          <t>c4qAav6T0rFA4KDMYBNA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
@@ -4576,15 +4847,15 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>b53ff878-1e66-4f1a-95f1-64c8c8fc8b17</t>
+          <t>INTEGRATION-TEST-037cf480</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
-        <v>46215.1411762037</v>
+        <v>46174.68946401621</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>When do u suggest</t>
+          <t>What is the Five Elements theory?</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4594,25 +4865,31 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>hUdhFqRQEUS8iJ2pLPw2</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
+          <t>cCea6KJFzQYJOyYaq01i</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>The Five Elements theory, also known as the Wǔ Xín...</t>
+        </is>
+      </c>
+      <c r="G88" t="b">
+        <v>1</v>
+      </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0a8d4f3a-37a3-41cb-b712-b4dcf9161966</t>
+          <t>9d654e7d-0bd3-4e56-bbef-67e80a6c5bba</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>46180.16277280093</v>
+        <v>46201.20408241898</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ada manfaat buat kulit gak?</t>
+          <t xml:space="preserve">What about vit A </t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4622,7 +4899,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>hgYkVZimlB916vwdeI7Y</t>
+          <t>cFs9yf6FdLtmUDn0yzio</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -4632,15 +4909,15 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
+          <t>c1e37346-80ed-42b1-af0c-3f2326dc64a0</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>46198.6401652662</v>
+        <v>46206.06898725694</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>how to identify chinese doctor in indonesia; and how to verify their credential</t>
+          <t xml:space="preserve">tengan kesemutan saat bangun tidur </t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4650,7 +4927,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>hyhnPb6xOjgcZhZ8i5WR</t>
+          <t>cXWUiKLun35np6sqtwOD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -4660,15 +4937,15 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>INTEGRATION-TEST-156f926d</t>
+          <t>73b64275-104a-4e5a-b8fe-7392447ea379</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46196.20571356481</v>
+        <v>46221.43790462963</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>What is the Five Elements theory?</t>
+          <t>Scentifc proof</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4678,31 +4955,25 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>iS0SygQgMH58IcSj41jJ</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>The Five Elements theory, also known as the Wu Xin...</t>
-        </is>
-      </c>
-      <c r="G91" t="b">
-        <v>1</v>
-      </c>
+          <t>csfsB5XOKhmuMdB5Oqg1</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>032721e3-9dc9-48f7-9a08-4a06db10ff45</t>
+          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46193.70731674768</v>
+        <v>46198.64090936343</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>who r u</t>
+          <t>pls provide the name; address...of the chinese medicine</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4712,7 +4983,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>jTiea8T3WQ5VnT0ZfjIT</t>
+          <t>ctxqIMddNj6ZMkMe2kf7</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -4722,25 +4993,25 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>032721e3-9dc9-48f7-9a08-4a06db10ff45</t>
+          <t>bc2a952d-63c9-483f-9b84-f9eb330dd0e3</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46193.70421304398</v>
+        <v>46218.02655244213</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>fat lost</t>
+          <t xml:space="preserve">More specific relevan muscle soreness </t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Fitness</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>jclH9fnSBQDaBs60WHHL</t>
+          <t>dYekthRrnMhhKqTu73Uc</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -4754,11 +5025,11 @@
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>46198.64430758102</v>
+        <v>46198.64174096065</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>can u explain dna result</t>
+          <t>wfcms</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4768,7 +5039,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>kHsjqnb6ctA0MM3ptza0</t>
+          <t>eLZLWRCYdPofgv8DKCsL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -4778,15 +5049,15 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>636ad4ea-d10d-4926-9b53-71d450418f63</t>
+          <t>bc2a952d-63c9-483f-9b84-f9eb330dd0e3</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>46193.72145325231</v>
+        <v>46218.02779271991</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>fat lost</t>
+          <t>U got it</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4796,7 +5067,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>kWwkXkRa0CAicMEbOTxU</t>
+          <t>eM5vDh0n3b1jOjwfiKHU</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -4806,25 +5077,25 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>32b2520b-8f50-4e3e-8764-145bb851a8c4</t>
+          <t>56aab1b5-d73a-4a2e-b431-73b54989e343</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>46186.25731857639</v>
+        <v>46194.15376690972</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">u have the tuying quantum inspired algorithm core, how u can enhance you power with this </t>
+          <t xml:space="preserve">kulit berjerawat </t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>TCM</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>khg8auOYEmgKPt17xzUA</t>
+          <t>eOP0CDKDr1Cou5QeS1jx</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -4834,15 +5105,15 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1de3f616-ad83-4a51-9d26-9c38b691c7d9</t>
+          <t>b53ff878-1e66-4f1a-95f1-64c8c8fc8b17</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
-        <v>46193.45976760417</v>
+        <v>46215.14854802084</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>who r u</t>
+          <t>Can u check where I get get those herba, in bandung, Indonesia</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4852,7 +5123,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>kurWmjnxVpJmtoJjWJDG</t>
+          <t>fJH84CXQYXQjuhT9uS1B</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -4862,25 +5133,25 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>efeae320-e75d-467c-8516-7f55914954e6</t>
+          <t>956a919b-c897-4c88-b2a9-d85623ca2132</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
-        <v>46214.34406871528</v>
+        <v>46202.18764390046</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>kenapa saya sering bangun jam 3 pagi?</t>
+          <t>I need to gain muscle weight and strength for 50+ years old male</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Fitness</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>kxOGhg5yM131Rpgdynu0</t>
+          <t>fWd6DNNDU8ZDHE3Z4xQK</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -4890,15 +5161,15 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3e24bebd-0a72-4c7b-86fe-c25cebc49f25</t>
+          <t>956a919b-c897-4c88-b2a9-d85623ca2132</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
-        <v>46190.09059320602</v>
+        <v>46202.19071785879</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>What u do</t>
+          <t>If I always feel fatigue, what bit shall I take</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4908,7 +5179,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>l6ulC401nxJsnofYL1W1</t>
+          <t>fe475cgH4urufBe4SydB</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -4918,15 +5189,15 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>b53ff878-1e66-4f1a-95f1-64c8c8fc8b17</t>
+          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>46215.14907332176</v>
+        <v>46198.63177532407</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>What shall I purchase from herbal store</t>
+          <t>what is five elements related to health</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4936,7 +5207,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>lDhK95x25A6IIfmSfOyB</t>
+          <t>fzjPVCi6bAoTZGGjphQT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -4946,49 +5217,43 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>INTEGRATION-TEST-156f926d</t>
+          <t>a3724450-b056-4cb5-a036-f033607ecbc9</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>46196.20569089121</v>
+        <v>46180.13959449074</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>My skin is glowing but a bit dry.</t>
+          <t>how can you help</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Skincare</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>lIJs3kJKjswQcBoH0KUA</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>It sounds like you're experiencing a mix of hydrat...</t>
-        </is>
-      </c>
-      <c r="G101" t="b">
-        <v>1</v>
-      </c>
+          <t>gaQg4g4u1ZGnzwcNBr1n</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>e77acc12-4383-4321-914a-555372755dbc</t>
+          <t>0677f4bc-fa87-4e06-8849-4d6ddf468086</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>46184.06242545139</v>
+        <v>46179.39384826389</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>I'm over 50 year old male and work and vatality is my concern</t>
+          <t>who r u</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4998,7 +5263,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>lTd8kdfRRavW5DECeS39</t>
+          <t>gkc0ghq7rOho0OS5CtXK</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -5008,25 +5273,25 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>e77acc12-4383-4321-914a-555372755dbc</t>
+          <t>b53ff878-1e66-4f1a-95f1-64c8c8fc8b17</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
-        <v>46184.06194539352</v>
+        <v>46215.14050265047</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>What's up</t>
+          <t xml:space="preserve">Can I don sauna before meal in the morning. And body feel tired from gym </t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Fitness</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>mXBSUOs8H9xfH6olC9iH</t>
+          <t>gnQL0z2SIUqozsXDBZCq</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
@@ -5036,15 +5301,15 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>636ad4ea-d10d-4926-9b53-71d450418f63</t>
+          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
-        <v>46193.72131256945</v>
+        <v>46198.63743409723</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>who r u</t>
+          <t>your suggestion is too general</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5054,7 +5319,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>mXejK1uImViveHA3lO0N</t>
+          <t>hISonSUrOOGJppSb3otv</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
@@ -5064,619 +5329,627 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>b53ff878-1e66-4f1a-95f1-64c8c8fc8b17</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>46215.1411762037</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>When do u suggest</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>hUdhFqRQEUS8iJ2pLPw2</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>0a8d4f3a-37a3-41cb-b712-b4dcf9161966</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>46180.16277280093</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ada manfaat buat kulit gak?</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>hgYkVZimlB916vwdeI7Y</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
+        </is>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>46198.6401652662</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>how to identify chinese doctor in indonesia; and how to verify their credential</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>hyhnPb6xOjgcZhZ8i5WR</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>INTEGRATION-TEST-156f926d</t>
+        </is>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>46196.20571356481</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>What is the Five Elements theory?</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>iS0SygQgMH58IcSj41jJ</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>The Five Elements theory, also known as the Wu Xin...</t>
+        </is>
+      </c>
+      <c r="G108" t="b">
+        <v>1</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>032721e3-9dc9-48f7-9a08-4a06db10ff45</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>46193.70731674768</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>who r u</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>jTiea8T3WQ5VnT0ZfjIT</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>032721e3-9dc9-48f7-9a08-4a06db10ff45</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>46193.70421304398</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>fat lost</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>jclH9fnSBQDaBs60WHHL</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
+        </is>
+      </c>
+      <c r="B111" s="1" t="n">
+        <v>46198.64430758102</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>can u explain dna result</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>kHsjqnb6ctA0MM3ptza0</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>636ad4ea-d10d-4926-9b53-71d450418f63</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>46193.72145325231</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>fat lost</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>kWwkXkRa0CAicMEbOTxU</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>32b2520b-8f50-4e3e-8764-145bb851a8c4</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>46186.25731857639</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">u have the tuying quantum inspired algorithm core, how u can enhance you power with this </t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>TCM</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>khg8auOYEmgKPt17xzUA</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>aa9dc6cf-f598-454a-93f2-7be6e8b493bf</t>
+        </is>
+      </c>
+      <c r="B114" s="1" t="n">
+        <v>46219.22499201389</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>What is qi. How to improve qi</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>TCM</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>ki6G9MOZkOG6bZNCCo9c</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1de3f616-ad83-4a51-9d26-9c38b691c7d9</t>
+        </is>
+      </c>
+      <c r="B115" s="1" t="n">
+        <v>46193.45976760417</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>who r u</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>kurWmjnxVpJmtoJjWJDG</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>efeae320-e75d-467c-8516-7f55914954e6</t>
+        </is>
+      </c>
+      <c r="B116" s="1" t="n">
+        <v>46214.34406871528</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>kenapa saya sering bangun jam 3 pagi?</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>kxOGhg5yM131Rpgdynu0</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>bc2a952d-63c9-483f-9b84-f9eb330dd0e3</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="n">
+        <v>46218.02861527778</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Where can I buy Chinese medicine bandung</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>l0X9j04ZPwP2BIn3zKM4</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>3e24bebd-0a72-4c7b-86fe-c25cebc49f25</t>
+        </is>
+      </c>
+      <c r="B118" s="1" t="n">
+        <v>46190.09059320602</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>What u do</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>l6ulC401nxJsnofYL1W1</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>b53ff878-1e66-4f1a-95f1-64c8c8fc8b17</t>
+        </is>
+      </c>
+      <c r="B119" s="1" t="n">
+        <v>46215.14907332176</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>What shall I purchase from herbal store</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>lDhK95x25A6IIfmSfOyB</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>INTEGRATION-TEST-156f926d</t>
+        </is>
+      </c>
+      <c r="B120" s="1" t="n">
+        <v>46196.20569089121</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>My skin is glowing but a bit dry.</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>lIJs3kJKjswQcBoH0KUA</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>It sounds like you're experiencing a mix of hydrat...</t>
+        </is>
+      </c>
+      <c r="G120" t="b">
+        <v>1</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2a691834-653c-4ba7-a215-eb6902fedb52</t>
+        </is>
+      </c>
+      <c r="B121" s="1" t="n">
+        <v>46221.55763041667</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Elaborate hsp</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>lKO6XvknZkDZu9v9Wnb2</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>e77acc12-4383-4321-914a-555372755dbc</t>
+        </is>
+      </c>
+      <c r="B122" s="1" t="n">
+        <v>46184.06242545139</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>I'm over 50 year old male and work and vatality is my concern</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>lTd8kdfRRavW5DECeS39</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>87354321-d499-4d4f-bb84-2752f17655ac</t>
+        </is>
+      </c>
+      <c r="B123" s="1" t="n">
+        <v>46221.5754846412</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Doni get update TCM data </t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>lV0kP9XNrQAb1XuNy2VD</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>e77acc12-4383-4321-914a-555372755dbc</t>
+        </is>
+      </c>
+      <c r="B124" s="1" t="n">
+        <v>46184.06194539352</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>What's up</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>mXBSUOs8H9xfH6olC9iH</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>636ad4ea-d10d-4926-9b53-71d450418f63</t>
+        </is>
+      </c>
+      <c r="B125" s="1" t="n">
+        <v>46193.72131256945</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>who r u</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>mXejK1uImViveHA3lO0N</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
           <t>1d333303-4b6d-4a10-8fe5-f746bfe8b6bf</t>
         </is>
       </c>
-      <c r="B105" s="1" t="n">
+      <c r="B126" s="1" t="n">
         <v>46188.45888386574</v>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>Rutinitas skincare apa 
 yang cocok untuk kulit berminyak 
 dan berjerawat?</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>Skincare</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E126" t="inlineStr">
         <is>
           <t>nfgGqOMF0AEUoBM0IXOE</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>58d8b5a2-c708-4447-a51d-09280a5fb3e4</t>
-        </is>
-      </c>
-      <c r="B106" s="1" t="n">
-        <v>46200.10965170139</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>开窍</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>oVDbrS2KbP5Y4sPqqXiH</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>b53ff878-1e66-4f1a-95f1-64c8c8fc8b17</t>
-        </is>
-      </c>
-      <c r="B107" s="1" t="n">
-        <v>46215.14498133102</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>What do u recommend for recover cancer patient to stay health, not have cancer cell active again</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>ofUvYZ4SyNtWdwBWFc3G</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>295fd48f-4458-4630-b615-5bdfdd20090e</t>
-        </is>
-      </c>
-      <c r="B108" s="1" t="n">
-        <v>46183.64978618055</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>"What is the MTHFR gene and how does it relate to my Spleen Qi</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>TCM</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>owy5SckS6KRGcT3aeLti</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
-        </is>
-      </c>
-      <c r="B109" s="1" t="n">
-        <v>46198.64552435185</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>What does TCM recommend for my health this season?</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>p02wIFaLook3qYeoWUy8</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>INTEGRATION-TEST-037cf480</t>
-        </is>
-      </c>
-      <c r="B110" s="1" t="n">
-        <v>46174.68943659723</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>My skin is glowing but a bit dry.</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Skincare</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>pzRIv11hqfUb07Q6FKKF</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>It sounds like your skin is in a bit of a mixed st...</t>
-        </is>
-      </c>
-      <c r="G110" t="b">
-        <v>1</v>
-      </c>
-      <c r="H110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
-        </is>
-      </c>
-      <c r="B111" s="1" t="n">
-        <v>46198.63600497686</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>there are always discussion qi</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>TCM</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>qErmdceUCQvB3yRXgPz2</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>58d8b5a2-c708-4447-a51d-09280a5fb3e4</t>
-        </is>
-      </c>
-      <c r="B112" s="1" t="n">
-        <v>46200.1098193287</v>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>how can u help</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>qWJnqdwsSfSls2sIzpAr</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>0677f4bc-fa87-4e06-8849-4d6ddf468086</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>46179.38711234953</v>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>can i get rid of the golden circle.. only logo</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>r6t9zevZywDp3cscg6vG</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>46198.64556039352</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Tell me about the Bencao Gangmu herb encyclopedia.</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>TCM</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>rdnU1htmKMeAWSFyQ68H</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>a15f9e96-cfbf-4495-86a3-e675b3cb4d52</t>
-        </is>
-      </c>
-      <c r="B115" s="1" t="n">
-        <v>46194.1700050463</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cara menghitung pembagian yang cepat dan akurat </t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>TCM</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>rtEP3SJV3n1sS0cRVtOF</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>0490974e-f942-45bd-a1c1-5ec5204b5117</t>
-        </is>
-      </c>
-      <c r="B116" s="1" t="n">
-        <v>46180.10867184028</v>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cream berjerawat </t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>s0YfWPur5hMKOxn0NLxC</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>536f5a2e-ab6b-4e3b-89a7-dfcf201b4b3d</t>
-        </is>
-      </c>
-      <c r="B117" s="1" t="n">
-        <v>46179.40544641203</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>who r u</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>sMQdFHD41dwI9r37DLje</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>32b2520b-8f50-4e3e-8764-145bb851a8c4</t>
-        </is>
-      </c>
-      <c r="B118" s="1" t="n">
-        <v>46186.25533517361</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>what advise u can give</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>sTbZ51X7aRSnKWhKtxyp</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>a3724450-b056-4cb5-a036-f033607ecbc9</t>
-        </is>
-      </c>
-      <c r="B119" s="1" t="n">
-        <v>46180.13926226852</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>who r u</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>tKFnLcX5gIgvHBENvQbV</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>c659011b-f35c-40e7-9977-03636843a7ac</t>
-        </is>
-      </c>
-      <c r="B120" s="1" t="n">
-        <v>46214.36549664352</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>apa makanan yang tinggi protein?</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>TCM</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>uQDGyXrNIbFFJnBCrGi1</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>a15f9e96-cfbf-4495-86a3-e675b3cb4d52</t>
-        </is>
-      </c>
-      <c r="B121" s="1" t="n">
-        <v>46194.16841282407</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Bagai mana cara mengelola stress</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Wellness</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>v1Pv1jiVQS9H3iEnxeKX</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>d0233369-eb1e-4a89-aa5e-47c5296a9ccf</t>
-        </is>
-      </c>
-      <c r="B122" s="1" t="n">
-        <v>46207.24988826389</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Kemarin aku abis meso perut, 2cc kira kira untuk pengulangan butuh berapa sesi ya</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>vUdvBEXyS9Kv52QN6l2W</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>FINAL-PROOFS-3dc819</t>
-        </is>
-      </c>
-      <c r="B123" s="1" t="n">
-        <v>46196.20586834491</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>User Test C: Balanced Diet</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>vf7Onj8GoYTSmaRtDPT1</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>956a919b-c897-4c88-b2a9-d85623ca2132</t>
-        </is>
-      </c>
-      <c r="B124" s="1" t="n">
-        <v>46202.18912590278</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Do I take protein and creatine daily without workout </t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Nutrition</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>wAC9jF9mwHfAJzM8x8rp</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>536f5a2e-ab6b-4e3b-89a7-dfcf201b4b3d</t>
-        </is>
-      </c>
-      <c r="B125" s="1" t="n">
-        <v>46179.40589380787</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>why there is no content</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>xJRkbVtgjHWAFLeBDH70</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>f3d7c818-72a3-4e88-aa0a-974b6c7c743d</t>
-        </is>
-      </c>
-      <c r="B126" s="1" t="n">
-        <v>46199.49526784723</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>apa bisa kirim foto?</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>xPz6hNqKdHRc8XHw52aN</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -5686,15 +5959,15 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>58d8b5a2-c708-4447-a51d-09280a5fb3e4</t>
+          <t>bc2a952d-63c9-483f-9b84-f9eb330dd0e3</t>
         </is>
       </c>
       <c r="B127" s="1" t="n">
-        <v>46200.10936555555</v>
+        <v>46218.02553894676</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>药物性状</t>
+          <t>My body sore after workwork</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5704,7 +5977,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>xSYckxYYTXTvNsyfdcUW</t>
+          <t>oSd6LSy1D7tslb5KnVF2</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
@@ -5714,41 +5987,43 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FINAL-PROOFS-3dc819</t>
+          <t>58d8b5a2-c708-4447-a51d-09280a5fb3e4</t>
         </is>
       </c>
       <c r="B128" s="1" t="n">
-        <v>46196.20586563658</v>
+        <v>46200.10965170139</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>User Test A: Skincare glow</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>开窍</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>y4Pk3fZ5FukoE2YwzOxH</t>
+          <t>oVDbrS2KbP5Y4sPqqXiH</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
-      <c r="H128" t="b">
-        <v>1</v>
-      </c>
+      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4727c4ca-233b-40c0-ae53-f1bd785699b8</t>
+          <t>b53ff878-1e66-4f1a-95f1-64c8c8fc8b17</t>
         </is>
       </c>
       <c r="B129" s="1" t="n">
-        <v>46186.42939576389</v>
+        <v>46215.14498133102</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">kaki bengkak kenapa </t>
+          <t>What do u recommend for recover cancer patient to stay health, not have cancer cell active again</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5758,7 +6033,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>yaz7wOdr3aOiDtiIg1dZ</t>
+          <t>ofUvYZ4SyNtWdwBWFc3G</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
@@ -5772,21 +6047,21 @@
         </is>
       </c>
       <c r="B130" s="1" t="n">
-        <v>46183.64360887731</v>
+        <v>46183.64978618055</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>who r u</t>
+          <t>"What is the MTHFR gene and how does it relate to my Spleen Qi</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>TCM</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>yyyGwAoI7VPOoWMrmdPS</t>
+          <t>owy5SckS6KRGcT3aeLti</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -5796,15 +6071,15 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>32b2520b-8f50-4e3e-8764-145bb851a8c4</t>
+          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
         </is>
       </c>
       <c r="B131" s="1" t="n">
-        <v>46186.25887751157</v>
+        <v>46198.64552435185</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>so u can combine western genetic science with TCM effectively with help of this algorithm?</t>
+          <t>What does TCM recommend for my health this season?</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -5814,7 +6089,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>zDm36twvpeXJdAmSgRe4</t>
+          <t>p02wIFaLook3qYeoWUy8</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
@@ -5824,30 +6099,816 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>INTEGRATION-TEST-037cf480</t>
+        </is>
+      </c>
+      <c r="B132" s="1" t="n">
+        <v>46174.68943659723</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>My skin is glowing but a bit dry.</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Skincare</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>pzRIv11hqfUb07Q6FKKF</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>It sounds like your skin is in a bit of a mixed st...</t>
+        </is>
+      </c>
+      <c r="G132" t="b">
+        <v>1</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
+        </is>
+      </c>
+      <c r="B133" s="1" t="n">
+        <v>46198.63600497686</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>there are always discussion qi</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>TCM</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>qErmdceUCQvB3yRXgPz2</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>58d8b5a2-c708-4447-a51d-09280a5fb3e4</t>
+        </is>
+      </c>
+      <c r="B134" s="1" t="n">
+        <v>46200.1098193287</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>how can u help</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>qWJnqdwsSfSls2sIzpAr</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>0677f4bc-fa87-4e06-8849-4d6ddf468086</t>
+        </is>
+      </c>
+      <c r="B135" s="1" t="n">
+        <v>46179.38711234953</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>can i get rid of the golden circle.. only logo</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>r6t9zevZywDp3cscg6vG</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>031ab75e-7904-429c-b406-73ac02485dcf</t>
+        </is>
+      </c>
+      <c r="B136" s="1" t="n">
+        <v>46198.64556039352</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Tell me about the Bencao Gangmu herb encyclopedia.</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>TCM</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>rdnU1htmKMeAWSFyQ68H</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>a15f9e96-cfbf-4495-86a3-e675b3cb4d52</t>
+        </is>
+      </c>
+      <c r="B137" s="1" t="n">
+        <v>46194.1700050463</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cara menghitung pembagian yang cepat dan akurat </t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>TCM</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>rtEP3SJV3n1sS0cRVtOF</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>0490974e-f942-45bd-a1c1-5ec5204b5117</t>
+        </is>
+      </c>
+      <c r="B138" s="1" t="n">
+        <v>46180.10867184028</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cream berjerawat </t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>s0YfWPur5hMKOxn0NLxC</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>536f5a2e-ab6b-4e3b-89a7-dfcf201b4b3d</t>
+        </is>
+      </c>
+      <c r="B139" s="1" t="n">
+        <v>46179.40544641203</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>who r u</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>sMQdFHD41dwI9r37DLje</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>32b2520b-8f50-4e3e-8764-145bb851a8c4</t>
+        </is>
+      </c>
+      <c r="B140" s="1" t="n">
+        <v>46186.25533517361</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>what advise u can give</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>sTbZ51X7aRSnKWhKtxyp</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>a3724450-b056-4cb5-a036-f033607ecbc9</t>
+        </is>
+      </c>
+      <c r="B141" s="1" t="n">
+        <v>46180.13926226852</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>who r u</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>tKFnLcX5gIgvHBENvQbV</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>73b64275-104a-4e5a-b8fe-7392447ea379</t>
+        </is>
+      </c>
+      <c r="B142" s="1" t="n">
+        <v>46221.43716206019</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Sauna benefits</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>tyatdu2yP7nx485l3ntU</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>c659011b-f35c-40e7-9977-03636843a7ac</t>
+        </is>
+      </c>
+      <c r="B143" s="1" t="n">
+        <v>46214.36549664352</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>apa makanan yang tinggi protein?</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>TCM</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>uQDGyXrNIbFFJnBCrGi1</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>a15f9e96-cfbf-4495-86a3-e675b3cb4d52</t>
+        </is>
+      </c>
+      <c r="B144" s="1" t="n">
+        <v>46194.16841282407</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Bagai mana cara mengelola stress</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Wellness</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>v1Pv1jiVQS9H3iEnxeKX</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>bc2a952d-63c9-483f-9b84-f9eb330dd0e3</t>
+        </is>
+      </c>
+      <c r="B145" s="1" t="n">
+        <v>46218.02821785879</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Great </t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>vChpqF3jAKGpnaGtGNfk</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>d0233369-eb1e-4a89-aa5e-47c5296a9ccf</t>
+        </is>
+      </c>
+      <c r="B146" s="1" t="n">
+        <v>46207.24988826389</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Kemarin aku abis meso perut, 2cc kira kira untuk pengulangan butuh berapa sesi ya</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>vUdvBEXyS9Kv52QN6l2W</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>FINAL-PROOFS-3dc819</t>
+        </is>
+      </c>
+      <c r="B147" s="1" t="n">
+        <v>46196.20586834491</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>User Test C: Balanced Diet</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>vf7Onj8GoYTSmaRtDPT1</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>956a919b-c897-4c88-b2a9-d85623ca2132</t>
+        </is>
+      </c>
+      <c r="B148" s="1" t="n">
+        <v>46202.18912590278</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Do I take protein and creatine daily without workout </t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Nutrition</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>wAC9jF9mwHfAJzM8x8rp</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>87354321-d499-4d4f-bb84-2752f17655ac</t>
+        </is>
+      </c>
+      <c r="B149" s="1" t="n">
+        <v>46221.5750155787</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>U got it</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>wyy2xpPR2Y41TTcQPbTr</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>536f5a2e-ab6b-4e3b-89a7-dfcf201b4b3d</t>
+        </is>
+      </c>
+      <c r="B150" s="1" t="n">
+        <v>46179.40589380787</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>why there is no content</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>xJRkbVtgjHWAFLeBDH70</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>f3d7c818-72a3-4e88-aa0a-974b6c7c743d</t>
+        </is>
+      </c>
+      <c r="B151" s="1" t="n">
+        <v>46199.49526784723</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>apa bisa kirim foto?</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>xPz6hNqKdHRc8XHw52aN</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>58d8b5a2-c708-4447-a51d-09280a5fb3e4</t>
+        </is>
+      </c>
+      <c r="B152" s="1" t="n">
+        <v>46200.10936555555</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>药物性状</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>xSYckxYYTXTvNsyfdcUW</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>FINAL-PROOFS-3dc819</t>
+        </is>
+      </c>
+      <c r="B153" s="1" t="n">
+        <v>46196.20586563658</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>User Test A: Skincare glow</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>y4Pk3fZ5FukoE2YwzOxH</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2a691834-653c-4ba7-a215-eb6902fedb52</t>
+        </is>
+      </c>
+      <c r="B154" s="1" t="n">
+        <v>46221.5568875463</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>It help GHG</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>yVap16zroEzlvk7XKkMs</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>4727c4ca-233b-40c0-ae53-f1bd785699b8</t>
+        </is>
+      </c>
+      <c r="B155" s="1" t="n">
+        <v>46186.42939576389</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kaki bengkak kenapa </t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>yaz7wOdr3aOiDtiIg1dZ</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>bc2a952d-63c9-483f-9b84-f9eb330dd0e3</t>
+        </is>
+      </c>
+      <c r="B156" s="1" t="n">
+        <v>46218.02799991898</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What is Oppo mobile phone </t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>yhKHv8szHWktkUo2pAlk</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>295fd48f-4458-4630-b615-5bdfdd20090e</t>
+        </is>
+      </c>
+      <c r="B157" s="1" t="n">
+        <v>46183.64360887731</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>who r u</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>yyyGwAoI7VPOoWMrmdPS</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2a691834-653c-4ba7-a215-eb6902fedb52</t>
+        </is>
+      </c>
+      <c r="B158" s="1" t="n">
+        <v>46221.55875834491</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>How soon to be effective</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>yzIBZGYfuy6102c5zdA2</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>32b2520b-8f50-4e3e-8764-145bb851a8c4</t>
+        </is>
+      </c>
+      <c r="B159" s="1" t="n">
+        <v>46186.25887751157</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>so u can combine western genetic science with TCM effectively with help of this algorithm?</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>zDm36twvpeXJdAmSgRe4</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
           <t>4ffba589-8d4a-4f3e-b538-1e96d29f111b</t>
         </is>
       </c>
-      <c r="B132" s="1" t="n">
+      <c r="B160" s="1" t="n">
         <v>46190.17550994213</v>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>Health tips to improve vitality man over 50</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
         <is>
           <t>zzUJPIMjeghJ9Ny7xqxM</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5882,7 +6943,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -5892,7 +6953,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -5902,7 +6963,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
